--- a/РАБОЧИЙ СТОЛ/расчет ПОКОМ КИ/Луганск/дв 21,07,26 лгрсч пок ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет ПОКОМ КИ/Луганск/дв 21,07,26 лгрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\21,07,26 ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ КИ\Луганск\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5201B43B-707C-4A2A-8114-A52EDE9B31E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CD9065-55F9-4991-8948-CE5608FBD1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,20 +19,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AM$141</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="336">
   <si>
     <t>дн</t>
   </si>
@@ -1878,7 +1870,7 @@
       </c>
       <c r="X5" s="4">
         <f t="shared" ref="X5:Y5" si="1">SUM(X6:X491)</f>
-        <v>-8082</v>
+        <v>-7266</v>
       </c>
       <c r="Y5" s="4">
         <f t="shared" si="1"/>
@@ -2040,7 +2032,7 @@
       </c>
       <c r="AL6" s="1"/>
       <c r="AM6" s="1">
-        <f t="shared" ref="AM6:AO37" si="7">ROUND(G6*W6,0)</f>
+        <f t="shared" ref="AM6:AM37" si="7">ROUND(G6*W6,0)</f>
         <v>209</v>
       </c>
       <c r="AN6" t="s">
@@ -5519,13 +5511,11 @@
         <f>V38+$W$1*U38</f>
         <v>812.21119999999871</v>
       </c>
-      <c r="X38" s="5">
-        <v>-815.99999999999989</v>
-      </c>
+      <c r="X38" s="5"/>
       <c r="Y38" s="5"/>
       <c r="Z38" s="1">
         <f t="shared" si="8"/>
-        <v>6.6417760617760617</v>
+        <v>10.58</v>
       </c>
       <c r="AA38" s="1">
         <f t="shared" ref="AA38:AA69" si="13">(F38+O38+P38+Q38+R38+S38+T38)/U38</f>
@@ -5563,7 +5553,7 @@
       </c>
       <c r="AL38" s="1"/>
       <c r="AM38" s="1">
-        <f t="shared" ref="AM38:AO69" si="14">ROUND(G38*W38,0)</f>
+        <f t="shared" ref="AM38:AM69" si="14">ROUND(G38*W38,0)</f>
         <v>325</v>
       </c>
       <c r="AN38" t="s">
@@ -9116,7 +9106,7 @@
         <v>119</v>
       </c>
       <c r="AM70" s="1">
-        <f t="shared" ref="AM70:AO101" si="22">ROUND(G70*W70,0)</f>
+        <f t="shared" ref="AM70:AM101" si="22">ROUND(G70*W70,0)</f>
         <v>0</v>
       </c>
       <c r="AN70" t="s">
@@ -12638,7 +12628,7 @@
         <v>119</v>
       </c>
       <c r="AM102" s="1">
-        <f t="shared" ref="AM102:AO133" si="29">ROUND(G102*W102,0)</f>
+        <f t="shared" ref="AM102:AM133" si="29">ROUND(G102*W102,0)</f>
         <v>0</v>
       </c>
       <c r="AO102" s="1">
@@ -16015,7 +16005,7 @@
         <v>289</v>
       </c>
       <c r="AM134" s="1">
-        <f t="shared" ref="AM134:AO141" si="33">ROUND(G134*W134,0)</f>
+        <f t="shared" ref="AM134:AM141" si="33">ROUND(G134*W134,0)</f>
         <v>0</v>
       </c>
       <c r="AN134" t="s">
@@ -31392,13 +31382,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F656E0-53D9-44C7-8AA3-4E5A4D245E1D}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="76.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="76.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>105</v>
       </c>
@@ -31415,8 +31406,17 @@
         <f>D1/C1</f>
         <v>-1944</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" t="s">
+        <v>322</v>
+      </c>
+      <c r="H1">
+        <v>-1944</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>109</v>
       </c>
@@ -31433,8 +31433,17 @@
         <f t="shared" ref="E2:E12" si="0">D2/C2</f>
         <v>-2951.9999999999995</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2" t="s">
+        <v>323</v>
+      </c>
+      <c r="H2">
+        <v>-1180.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>113</v>
       </c>
@@ -31452,7 +31461,7 @@
         <v>-815.99999999999989</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>134</v>
       </c>
@@ -31469,8 +31478,17 @@
         <f t="shared" si="0"/>
         <v>-600</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" t="s">
+        <v>325</v>
+      </c>
+      <c r="H4">
+        <v>-240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -31487,8 +31505,17 @@
         <f t="shared" si="0"/>
         <v>-522</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>168</v>
+      </c>
+      <c r="G5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H5">
+        <v>-208.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>128</v>
       </c>
@@ -31505,8 +31532,17 @@
         <f t="shared" si="0"/>
         <v>-336</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" t="s">
+        <v>327</v>
+      </c>
+      <c r="H6">
+        <v>-134.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>227</v>
       </c>
@@ -31523,8 +31559,17 @@
         <f t="shared" si="0"/>
         <v>-300</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>227</v>
+      </c>
+      <c r="G7" t="s">
+        <v>328</v>
+      </c>
+      <c r="H7">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>242</v>
       </c>
@@ -31541,8 +31586,17 @@
         <f t="shared" si="0"/>
         <v>-258.00000000000006</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G8" t="s">
+        <v>329</v>
+      </c>
+      <c r="H8">
+        <v>-77.400000000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>202</v>
       </c>
@@ -31559,8 +31613,17 @@
         <f t="shared" si="0"/>
         <v>-156</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" t="s">
+        <v>330</v>
+      </c>
+      <c r="H9">
+        <v>-54.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>126</v>
       </c>
@@ -31577,8 +31640,17 @@
         <f t="shared" si="0"/>
         <v>-72</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H10">
+        <v>-28.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>148</v>
       </c>
@@ -31595,8 +31667,17 @@
         <f t="shared" si="0"/>
         <v>-65.999999999999986</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G11" t="s">
+        <v>332</v>
+      </c>
+      <c r="H11">
+        <v>-26.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>146</v>
       </c>
@@ -31612,6 +31693,15 @@
       <c r="E12">
         <f t="shared" si="0"/>
         <v>-60</v>
+      </c>
+      <c r="F12" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" t="s">
+        <v>333</v>
+      </c>
+      <c r="H12">
+        <v>-24</v>
       </c>
     </row>
   </sheetData>
